--- a/etf_holdings/2026-09-16_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-16_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,52 +1053,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>0006</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>60SK HYNIX INC</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>60SK HYNIX INC</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1.93%</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.25%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>0.85%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-1.08%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>16304</v>
+      </c>
       <c r="K11" t="n">
-        <v>760000</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+        <v>7445</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-8,859</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-09-15_00403A_full_holdings.xlsx</t>
+          <t>2026-09-15_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1108,60 +1126,60 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>0091</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>50SAMSUNG ELECTRO-MECHANICS CO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>50SAMSUNG ELECTRO-MECHANICS CO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.65%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-1.06%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>35000</v>
+        <v>18688</v>
       </c>
       <c r="K12" t="n">
-        <v>45000</v>
+        <v>7234</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>-11,454</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-15_00403A_full_holdings.xlsx</t>
+          <t>2026-09-15_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1171,60 +1189,60 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>IBIDEN CO LTD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>IBIDEN CO LTD</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3700000</v>
+        <v>130900</v>
       </c>
       <c r="K13" t="n">
-        <v>3850000</v>
+        <v>83000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>150,000</t>
+          <t>-47,900</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-09-15_00403A_full_holdings.xlsx</t>
+          <t>2026-09-15_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1234,456 +1252,141 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6981</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>MURATA MANUFACTURING CO LTD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>MURATA MANUFACTURING CO LTD</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1100000</v>
+        <v>477100</v>
       </c>
       <c r="K14" t="n">
-        <v>1102000</v>
+        <v>351900</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>-125,200</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-09-15_00403A_full_holdings.xlsx</t>
+          <t>2026-09-15_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3533</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>嘉澤</t>
-        </is>
-      </c>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>嘉澤</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0.20%</t>
-        </is>
-      </c>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.16%</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-0.04%</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>200000</v>
-      </c>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>160000</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>-40,000</t>
-        </is>
-      </c>
+        <v>1000000</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-09-15_00403A_full_holdings.xlsx</t>
+          <t>2026-09-15_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0006</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>60SK HYNIX INC</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>60SK HYNIX INC</t>
-        </is>
-      </c>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.93%</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.85%</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-1.08%</t>
-        </is>
-      </c>
+          <t>0.90%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>16304</v>
-      </c>
-      <c r="K16" t="n">
-        <v>7445</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-8,859</t>
-        </is>
-      </c>
+        <v>246000</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
-        <is>
-          <t>2026-09-15_00990A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>0091</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>50SAMSUNG ELECTRO-MECHANICS CO</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>50SAMSUNG ELECTRO-MECHANICS CO</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>1.71%</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.65%</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-1.06%</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>18688</v>
-      </c>
-      <c r="K17" t="n">
-        <v>7234</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>-11,454</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2026-09-15_00990A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4062</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>IBIDEN CO LTD</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>IBIDEN CO LTD</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>1.46%</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0.93%</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-0.53%</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>130900</v>
-      </c>
-      <c r="K18" t="n">
-        <v>83000</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>-47,900</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2026-09-15_00990A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>6981</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>MURATA MANUFACTURING CO LTD</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>MURATA MANUFACTURING CO LTD</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2.00%</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>1.48%</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-0.52%</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>477100</v>
-      </c>
-      <c r="K19" t="n">
-        <v>351900</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>-125,200</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2026-09-15_00990A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>0.76%</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2026-09-15_00407A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>8210</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>勤誠</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0.90%</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="n">
-        <v>246000</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
         <is>
           <t>2026-09-15_00407A_full_holdings.xlsx</t>
         </is>
